--- a/data/Enrollment_2026-07-20.xlsx
+++ b/data/Enrollment_2026-07-20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soyeonahn/Library/CloudStorage/GoogleDrive-s.ahn@miami.edu/My Drive/SEHD_VD/Academic affairs/Graduate Enrollment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A377FC48-FBBD-8140-985C-1F261FB722C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3B28577-984A-A846-A139-6E0CE06B534F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44700" yWindow="14600" windowWidth="36000" windowHeight="21700" xr2:uid="{2DAD95BE-F879-D340-BEDF-B079FDCBFA41}"/>
+    <workbookView xWindow="53700" yWindow="9380" windowWidth="36000" windowHeight="21700" xr2:uid="{2DAD95BE-F879-D340-BEDF-B079FDCBFA41}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -647,11 +647,11 @@
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" si="1"/>
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3">
         <v>0</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="J5" s="2">
         <f t="shared" si="2"/>
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -809,11 +809,11 @@
       </c>
       <c r="C10" s="8">
         <f t="shared" si="3"/>
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D10" s="9">
         <f t="shared" si="3"/>
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E10" s="8">
         <f t="shared" si="3"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="J10" s="9">
         <f>SUM(J3:J9)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K10" s="11">
         <f>I10*1.3</f>
@@ -844,7 +844,7 @@
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K11" s="13">
         <f>K10-D10</f>
-        <v>14.700000000000017</v>
+        <v>12.700000000000017</v>
       </c>
     </row>
   </sheetData>
